--- a/human_resources_forms/029_software_developer_interview_form--human_resources_forms.xlsx
+++ b/human_resources_forms/029_software_developer_interview_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -973,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1103,17 +1103,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>languages_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>c++</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>HTML</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>css</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>CSS</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>css</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>SQL</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>node.js</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Node.js</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>node.js</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Node.js</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>react</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>React</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>react</t>
+          <t>ui/ux</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>UI/UX</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ui/ux</t>
+          <t>git</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Git</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>git</t>
+          <t>svn</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>SVN</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>svn</t>
+          <t>agile</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>Agile</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>agile</t>
+          <t>scrum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Agile</t>
+          <t>Scrum</t>
         </is>
       </c>
     </row>
@@ -1295,29 +1295,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>scrum</t>
+          <t>kanban</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scrum</t>
+          <t>Kanban</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>previous_workplace_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>kanban</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kanban</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>ibm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ibm</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1431,44 +1431,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ibm</t>
+          <t>dell</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>previous_workplace_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>previous_workplace_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>dell</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
